--- a/學習站點/守道.xlsx
+++ b/學習站點/守道.xlsx
@@ -16,28 +16,41 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>1.人生于世,當有所守,守心不出錯,守嘴不惹禍.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>3.待人寬宏,處事大度,自然得人心.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.凡事有交代、件件有着落,事事有回音.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.凡事能商量,便是能尊重别人的意愿,不将自己的意志和观点强加到别人身上.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.预先防止，做好预案.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>2.知人不評人,知事不聲張,才能行穩致遠.</t>
-  </si>
-  <si>
-    <t>3.待人寬宏,處事大度,自然得人心.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5.凡事有交代、件件有着落,事事有回音.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.凡事能商量,便是能尊重别人的意愿,不将自己的意志和观点强加到别人身上.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.预先防止，做好预案.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.以德立身,泽己及人. 譯文：道德没有统一的标准,德的前提就是尽量去帮助别人,做有利于自己和他人的事,而不损人利己.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8.在处于劣势或不得志时，为了将来的发展，应该以屈待伸，忍得一时之忿，这是趋吉避凶的智慧，也是圆融无碍的做人之道。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>9.方圆做人，要谨记在原则问题上只能处之以方，要强硬地坚持自己的原则。否则，做人就很容易失去方向，做事也难获成功。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -382,10 +395,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="86.75" customWidth="1"/>
+    <col min="1" max="1" width="117.125" customWidth="1"/>
     <col min="2" max="2" width="68.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -394,25 +407,36 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
